--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T10:31:14+00:00</t>
+    <t>2026-02-04T11:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Goal|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Goal</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -458,11 +458,11 @@
     <t>referenceProjetPerso</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference}
 </t>
   </si>
   <si>
-    <t>Lien vers le projet personnalisé</t>
+    <t>TDDUI CarePlan Projet Perso Ref</t>
   </si>
   <si>
     <t>Liens vers le projet personnalisé, utilisables dans le profil TDDUIGoalObjectif.</t>
@@ -481,11 +481,11 @@
     <t>pieceJointeAttente</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -936,7 +936,7 @@
     <t>Goal.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1202,11 +1202,11 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator}
 </t>
   </si>
   <si>
-    <t>TDDUI Discriminator Extension</t>
+    <t>TDDUI Discriminator</t>
   </si>
   <si>
     <t>Extension pour discriminer les éléments CarePlan.supportingInfo et Goal.note.</t>
@@ -1337,13 +1337,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="origineAttente"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-attente-note-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-attente-note</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1390,7 +1390,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="commentaireAttente"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1751,7 +1751,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1766,7 +1766,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="131.83984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.23046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
